--- a/jpcore-r4/main/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3914" uniqueCount="636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3914" uniqueCount="633">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.2</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -313,10 +313,10 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
+    <t>リソースに関するMetadata</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
   </si>
   <si>
     <t>Resource.meta</t>
@@ -352,7 +352,7 @@
 </t>
   </si>
   <si>
-    <t>「リソースコンテンツの言語」</t>
+    <t>リソースコンテンツの言語</t>
   </si>
   <si>
     <t>リソースが書かれている基本言語。</t>
@@ -364,7 +364,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>「人間の言語。」</t>
+    <t>人間の言語。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -410,7 +410,7 @@
 </t>
   </si>
   <si>
-    <t>「含まれている、インラインのリソース」</t>
+    <t>含まれている、インラインのリソース</t>
   </si>
   <si>
     <t>これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。</t>
@@ -472,7 +472,7 @@
 </t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -549,7 +549,7 @@
 user content</t>
   </si>
   <si>
-    <t>無視できない拡張機能 (Mushi dekinai kakuchou kinou)</t>
+    <t>無視できない拡張機能</t>
   </si>
   <si>
     <t>リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。</t>
@@ -662,19 +662,19 @@
     <t>通常|公式|一時的|セカンダリ|古い（知られている場合） / usual | official | temp | secondary | old (If known)</t>
   </si>
   <si>
-    <t>この識別子の目的。 / The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>アプリケーションは、識別子が一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>特定の使用のコンテキストが一連の識別子の中から選択される適切な識別子を許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+    <t>このidentifierの目的。 / The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>アプリケーションは、identifierが一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>特定の使用のコンテキストが一連のidentifierの中から選択される適切なidentifierを許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
   </si>
   <si>
     <t>required</t>
   </si>
   <si>
-    <t>既知の場合、この識別子の目的を識別します。 / Identifies the purpose for this identifier, if known .</t>
+    <t>既知の場合、このidentifierの目的を識別します。 / Identifies the purpose for this identifier, if known .</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
@@ -683,7 +683,7 @@
     <t>Identifier.use</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -700,22 +700,22 @@
 </t>
   </si>
   <si>
-    <t>識別子の説明 / Description of identifier</t>
-  </si>
-  <si>
-    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>この要素は、識別子の一般的なカテゴリのみを扱います。識別子。システムに対応するコードに使用しないでください。一部の識別子は、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明な識別子を処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>識別子システムが不明な場合、ユーザーは識別子を使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
+    <t>identifierの説明 / Description of identifier</t>
+  </si>
+  <si>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>この要素は、identifierの一般的なカテゴリのみを扱います。identifier。システムに対応するコードに使用しないでください。一部のidentifierは、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明なidentifierを処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>identifierシステムが不明な場合、ユーザーはidentifierを使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
     <t>extensible</t>
   </si>
   <si>
-    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
@@ -736,16 +736,16 @@
     <t>Rp番号(剤グループ番号)についてのsystem値</t>
   </si>
   <si>
-    <t>ここで付番されたIDがRp番号であることを明示するためにOIDとして定義された。urn:oid:1.2.392.100495.20.3.81で固定される。</t>
-  </si>
-  <si>
-    <t>識別子。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
-  </si>
-  <si>
-    <t>urn:oid:1.2.392.100495.20.3.81</t>
+    <t>ここで付番されたIDがRp番号であることを明示するためにOID-urlとして定義された。http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumberで固定される。</t>
+  </si>
+  <si>
+    <t>identifier。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>identifierのセットがたくさんあります。2つのidentifierを一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意のidentifierセットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumber</t>
   </si>
   <si>
     <t>Identifier.system</t>
@@ -794,7 +794,7 @@
     <t>IDが使用に有効だった時間期間 / Time period when id is/was valid for use</t>
   </si>
   <si>
-    <t>識別子が使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
+    <t>identifierが使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
     <t>Identifier.period</t>
@@ -819,10 +819,10 @@
     <t>IDを発行した組織（単なるテキストである可能性があります） / Organization that issued id (may be just text)</t>
   </si>
   <si>
-    <t>識別子を発行/管理する組織。 / Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>識別子は、.reference要素を省略し、割り当て組織に関する名前またはその他のテキスト情報を反映した.display要素のみを含む場合があります。 / The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+    <t>identifierを発行/管理する組織。 / Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>identifierは、.reference要素を省略し、割り当て組織に関する名前またはその他のテキスト情報を反映した.display要素のみを含む場合があります。 / The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
   </si>
   <si>
     <t>Identifier.assigner</t>
@@ -846,7 +846,7 @@
     <t>薬剤をオーダする単位としての処方箋に対するID。原則として投薬実施の基となったMedicationRequestのIDを設定する。</t>
   </si>
   <si>
-    <t>これはビジネス識別子であり、リソース識別子ではありません。</t>
+    <t>これはビジネスidentifierであり、リソースidentifierではありません。</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier:requestIdentifier.id</t>
@@ -864,13 +864,13 @@
     <t>MedicationAdministration.identifier:requestIdentifier.system</t>
   </si>
   <si>
-    <t>識別子値の名前空間 / The namespace for the identifier value</t>
+    <t>identifier値の名前空間 / The namespace for the identifier value</t>
   </si>
   <si>
     <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
+    <t>urn:oid:1.2.392.100495.20.3.11</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier:requestIdentifier.value</t>
@@ -879,10 +879,10 @@
     <t>一意の値 / The value that is unique</t>
   </si>
   <si>
-    <t>通常、識別子の部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>通常、identifierの部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。identifier。価値は、identifierの知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier:requestIdentifier.period</t>
@@ -968,7 +968,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>"医薬品投与が取り消された理由を示すコードのセット"</t>
+    <t>医薬品投与が取り消された理由を示すコードのセット</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/reason-medication-not-given-codes</t>
@@ -1011,7 +1011,7 @@
     <t>医薬品</t>
   </si>
   <si>
-    <t>投与された薬剤を識別する。既知の薬のリストから薬を識別するコード情報を設定する。</t>
+    <t>医薬品の識別情報は必須でありmedicationReference.referenceが必ず存在しなければならない、JP Coreでは注射の医薬品情報は単一薬剤の場合も Medicationリソースとして記述し、medicationCodeableConceptは使用しない。参照するMedicationリソースは、MedicationRequest.contained属性に内包することが望ましいが、外部参照としても良い。</t>
   </si>
   <si>
     <t>ひとつのtext要素と、複数のcoding 要素を記述できる。処方オーダ時に選択または入力し、実際に処方箋に印字される文字列を必ずtext要素に格納した上で、それをコード化した情報を1個以上のcoding 要素に記述する。  
@@ -1041,10 +1041,10 @@
 </t>
   </si>
   <si>
-    <t>「誰が薬を受け取りましたか？」</t>
-  </si>
-  <si>
-    <t>薬を受け取る人、動物、またはグループ。 (Kusuri wo uketoru hito, doubutsu, matawa guruupu.)</t>
+    <t>誰が薬を受け取りましたか？</t>
+  </si>
+  <si>
+    <t>薬を受け取る人、動物、またはグループ。</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1107,7 +1107,7 @@
 Period</t>
   </si>
   <si>
-    <t>「管理の開始時刻と終了時刻」</t>
+    <t>管理の開始時刻と終了時刻</t>
   </si>
   <si>
     <t>与えられた属性が「真実」となっている場合に、行政が行われた（または行われなかった）特定の日時または時間の間隔。錠剤の服用など、多くの行政では、dateTimeの使用が適切です。</t>
@@ -1188,10 +1188,10 @@
     <t>MedicationAdministration.performer.function</t>
   </si>
   <si>
-    <t>「パフォーマンスの種類」</t>
-  </si>
-  <si>
-    <t>演者の医薬品投与における関与タイプを区別します。 (Ensha no iyakuhin tōyo ni okeru kan'yo taipu o kubetsushimasu.)</t>
+    <t>パフォーマンスの種類</t>
+  </si>
+  <si>
+    <t>演者の医薬品投与における関与タイプを区別します。</t>
   </si>
   <si>
     <t>薬物管理を行った個人の役割を説明するコード</t>
@@ -1213,7 +1213,7 @@
 </t>
   </si>
   <si>
-    <t>「薬剤投与を行ったのは誰ですか？」</t>
+    <t>薬剤投与を行ったのは誰ですか？</t>
   </si>
   <si>
     <t>薬剤投与を行った人物または物品を示す</t>
@@ -1228,7 +1228,7 @@
     <t>MedicationAdministration.reasonCode</t>
   </si>
   <si>
-    <t>理由に基づく行政処理 (Riyuu ni motozuku gyousei shori)</t>
+    <t>理由に基づく行政処理</t>
   </si>
   <si>
     <t>与えられた薬を説明するコード。</t>
@@ -1284,7 +1284,7 @@
 </t>
   </si>
   <si>
-    <t>"リクエスト管理対象として実行してください。" (Rikuesuto kanri taishou toshite jikkou shite kudasai.)</t>
+    <t>リクエスト管理対象として実行してください。</t>
   </si>
   <si>
     <t>管理を実行するための元の要求、指示、または権限。</t>
@@ -1328,7 +1328,7 @@
 </t>
   </si>
   <si>
-    <t>「行政に関する情報」</t>
+    <t>行政に関する情報</t>
   </si>
   <si>
     <t>他の属性では伝えられない薬剤投与に関する追加情報</t>
@@ -1715,7 +1715,7 @@
     <t>シンボルの定義のソースについて明確である必要があります。 / Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.200250.2.2.20.30</t>
+    <t>http://jami.jp/CodeSystem/MedicationMethodBasicUsage</t>
   </si>
   <si>
     <t>Coding.system</t>
@@ -1839,7 +1839,7 @@
     <t>投与⽅法に対応するJAMI 用法コード表基本用法2桁コード</t>
   </si>
   <si>
-    <t>投与⽅法に対応するJAMI 用法コード表基本用法2桁コードを識別するURI。２桁コードurn:oid:1.2.392.200250.2.2.20.40</t>
+    <t>投与⽅法に対応するJAMI 用法コード表基本用法2桁コードを識別するURI。２桁コードhttp://jami.jp/CodeSystem/MedicationUsage</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIDetailUsage_VS</t>
@@ -1854,7 +1854,7 @@
     <t>MedicationAdministration.dosage.method.coding:unitDigit2.system</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.200250.2.2.20.40</t>
+    <t>http://jami.jp/CodeSystem/MedicationMethodDetailUsage</t>
   </si>
   <si>
     <t>MedicationAdministration.dosage.method.coding:unitDigit2.version</t>
@@ -1897,17 +1897,13 @@
     <t>1回の投与イベントで投与される薬剤の量。この値は、投与が錠剤の飲み込みや注射などの本質的に瞬間的なイベントである場合に使用する。</t>
   </si>
   <si>
-    <t>薬剤に関する簡易的な数量と単位を定めている。ValueおよびCodeを必須とし、comparatorは記述不可。単位についてはMERIT9医薬品単位略号の利用を推進している。(**SHOULD**)</t>
-  </si>
-  <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-qty-3:ユニットのコードが存在する場合、システムも存在するものとします / If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:コンパレータは、単純なQuantityで使用されません / The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
-  </si>
-  <si>
-    <t>PQ, IVL&lt;PQ&gt;, MO, CO, depending on the values</t>
-  </si>
-  <si>
-    <t>SN (see also Range) or CQ</t>
+    <t>もし投与速度が即時でない場合、単回の投与期間中に投与される総量を示すことができます。</t>
+  </si>
+  <si>
+    <t>.doseQuantity</t>
+  </si>
+  <si>
+    <t>RXA-6 Administered Amount / RXA-7 Administered Units</t>
   </si>
   <si>
     <t>MedicationAdministration.dosage.rate[x]</t>
@@ -1950,17 +1946,13 @@
 </t>
   </si>
   <si>
-    <t>単位時間内での薬剤の容量</t>
-  </si>
-  <si>
-    <t>比率データタイプは、関係を数量と共通単位を使用して適切に表現できない場合にのみ、2つの数値の関係を表現するために使用する必要があります。分母値が「1」に固定されていることが知られている場合、比率ではなく数量を使用する必要があります。 / The Ratio datatype should only be used to express a relationship of two numbers if the relationship cannot be suitably expressed using a Quantity and a common unit.  Where the denominator value is known to be fixed to "1", Quantity should be used instead of Ratio.</t>
-  </si>
-  <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-rat-1:分子と分母の両方が存在するか、両方が存在します。両方が欠席している場合、いくつかの拡張が存在するものとします / Numerator and denominator SHALL both be present, or both are absent. If both are absent, there SHALL be some extension present {(numerator.empty() xor denominator.exists()) and (numerator.exists() or extension.exists())}</t>
-  </si>
-  <si>
-    <t>RTO</t>
+    <t>時間当たりの投与量</t>
+  </si>
+  <si>
+    <t>患者に投与されたあるいは投与される薬剤の導入速度を特定します。通常、投与速度は、100 ml / 1時間、または100 ml /時間（時間あたり100 ml）のような輸液の速度として表されます。時間単位あたりの速度として表される場合もあります。例えば、500 ml / 2時間のように。その他の例：200 mcg /分あるいは1分間当たり200 mcg；1リットル/8時間。</t>
+  </si>
+  <si>
+    <t>もしレートが時間の経過とともに変化する場合、かつそれをMedicationAdministrationに取り込む場合は、それぞれの変化を特定のMedicationAdministration.dosage.rateと、レート変更が発生した日時で捉える必要があります。通常、MedicationAdministration.dosage.rate要素は平均レートを伝えるために使用されません。</t>
   </si>
   <si>
     <t>MedicationAdministration.dosage.rate[x]:rateQuantity</t>
@@ -1974,9 +1966,6 @@
   </si>
   <si>
     <t>投与速度(流量)を指定する単位は流量を表す単位（e.g. 量/時間)を指定する</t>
-  </si>
-  <si>
-    <t>使用のコンテキストは、これがどのような量であるか、したがってどのようなユニットを使用できるかを頻繁に定義する場合があります。使用のコンテキストは、コンパレータの値を制限する場合もあります。 / The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
   </si>
   <si>
     <t>MedicationAdministration.eventHistory</t>
@@ -2326,7 +2315,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="145.265625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="155.12109375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="69.23046875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -14120,22 +14109,22 @@
         <v>89</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ101" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL101" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="AK101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL101" t="s" s="2">
+      <c r="AM101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN101" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="AM101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN101" t="s" s="2">
-        <v>608</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>79</v>
@@ -14143,10 +14132,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14169,16 +14158,16 @@
         <v>79</v>
       </c>
       <c r="K102" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="L102" t="s" s="2">
         <v>610</v>
       </c>
-      <c r="L102" t="s" s="2">
+      <c r="M102" t="s" s="2">
         <v>611</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>612</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>613</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14216,17 +14205,17 @@
         <v>79</v>
       </c>
       <c r="AB102" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="AC102" s="2"/>
       <c r="AD102" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14244,13 +14233,13 @@
         <v>79</v>
       </c>
       <c r="AL102" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN102" t="s" s="2">
         <v>616</v>
-      </c>
-      <c r="AM102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN102" t="s" s="2">
-        <v>617</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>79</v>
@@ -14258,13 +14247,13 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="C103" t="s" s="2">
         <v>618</v>
-      </c>
-      <c r="B103" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="C103" t="s" s="2">
-        <v>619</v>
       </c>
       <c r="D103" t="s" s="2">
         <v>79</v>
@@ -14286,10 +14275,10 @@
         <v>79</v>
       </c>
       <c r="K103" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="L103" t="s" s="2">
         <v>620</v>
-      </c>
-      <c r="L103" t="s" s="2">
-        <v>621</v>
       </c>
       <c r="M103" t="s" s="2">
         <v>621</v>
@@ -14345,7 +14334,7 @@
         <v>79</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14354,22 +14343,22 @@
         <v>89</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>623</v>
+        <v>101</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>624</v>
+        <v>615</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>132</v>
+        <v>616</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>79</v>
@@ -14377,13 +14366,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="D104" t="s" s="2">
         <v>79</v>
@@ -14405,16 +14394,16 @@
         <v>79</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>629</v>
+        <v>622</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -14464,7 +14453,7 @@
         <v>79</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -14473,22 +14462,22 @@
         <v>89</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>606</v>
+        <v>101</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>607</v>
+        <v>615</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>608</v>
+        <v>616</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>79</v>
@@ -14496,10 +14485,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14522,16 +14511,16 @@
         <v>79</v>
       </c>
       <c r="K105" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="N105" t="s" s="2">
         <v>631</v>
-      </c>
-      <c r="L105" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>634</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14581,7 +14570,7 @@
         <v>79</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -14599,7 +14588,7 @@
         <v>79</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>79</v>

--- a/jpcore-r4/main/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/main/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a</t>
+    <t>1.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30</t>
+    <t>2025-07-04</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -268,7 +268,7 @@
     <t>患者への注射薬剤投与記録</t>
   </si>
   <si>
-    <t>患者が薬剤を服用する、あるいは投与される事象を説明します。これは、錠剤を飲むだけだったり、長時間の点滴だったりすることがあります。関連するリソースは、この事象を許可された処方箋や、患者と医療従事者の具体的なEncounter（診察、受診、入退院など）と結びつけます。</t>
+    <t>患者が薬剤を服用する、あるいは投与される事象を説明します。これは、錠剤を飲むだけだったり、長時間の点滴だったりすることがあります。関連するリソースは、この事象を許可された処方箋や、患者と医療従事者の具体的な受療行動と結びつけます。</t>
   </si>
   <si>
     <t>dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません (moshi risōsu ga hoka no risōsu ni fukumarete iru baai, sono risōsu ni wa nesuto sareta risōsu o fukumete wa narimasen). {contained.contained.empty()}
@@ -449,7 +449,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>MedicationAdministration.extension:requestDepartment</t>

--- a/jpcore-r4/main/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -1491,7 +1491,7 @@
     <t>bodySite</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {bodySite}
+    <t xml:space="preserve">Extension {bodySite|5.2.0}
 </t>
   </si>
   <si>
@@ -2291,17 +2291,17 @@
   <dimension ref="A1:AO105"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="68.30859375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="58.66015625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="23.1328125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="58.5625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="50.2890625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="19.83203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="111.4140625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="95.515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2310,27 +2310,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="155.12109375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="69.23046875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="45.6171875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="132.98828125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="59.3515625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="39.109375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="101.08984375" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="22.50390625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="245.42578125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="86.66796875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="19.29296875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10275,7 +10275,7 @@
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>79</v>

--- a/jpcore-r4/main/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/main/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -1491,7 +1491,7 @@
     <t>bodySite</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {bodySite|5.2.0}
+    <t xml:space="preserve">Extension {bodySite|5.3.0-ballot-tc1}
 </t>
   </si>
   <si>

--- a/jpcore-r4/main/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -367,7 +367,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -718,7 +718,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -812,7 +812,7 @@
     <t>MedicationAdministration.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -909,7 +909,7 @@
     <t>MedicationAdministration.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|Procedure)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|Procedure|4.0.1)
 </t>
   </si>
   <si>
@@ -971,7 +971,7 @@
     <t>医薬品投与が取り消された理由を示すコードのセット</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/reason-medication-not-given-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/reason-medication-not-given-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -995,7 +995,7 @@
     <t>薬剤の投与が予想される場所を記述するコード化された概念。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-admin-category</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-admin-category|4.0.1</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication usage"].value</t>
@@ -1037,7 +1037,7 @@
     <t>MedicationAdministration.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Group|4.0.1)
 </t>
   </si>
   <si>
@@ -1062,7 +1062,7 @@
     <t>MedicationAdministration.context</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|EpisodeOfCare)
+    <t xml:space="preserve">Reference(Encounter|4.0.1|EpisodeOfCare|4.0.1)
 </t>
   </si>
   <si>
@@ -1087,7 +1087,7 @@
     <t>MedicationAdministration.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1197,7 +1197,7 @@
     <t>薬物管理を行った個人の役割を説明するコード</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/med-admin-perform-function</t>
+    <t>http://hl7.org/fhir/ValueSet/med-admin-perform-function|4.0.1</t>
   </si>
   <si>
     <t>Event.performer.function</t>
@@ -1209,7 +1209,7 @@
     <t>MedicationAdministration.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Patient|RelatedPerson|Device)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Device|4.0.1)
 </t>
   </si>
   <si>
@@ -1237,7 +1237,7 @@
     <t>薬剤投与が行われた理由を示すコードのセット。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/reason-medication-given-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/reason-medication-given-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1252,7 +1252,7 @@
     <t>MedicationAdministration.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Observation|DiagnosticReport)
+    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1)
 </t>
   </si>
   <si>
@@ -1280,7 +1280,7 @@
     <t>MedicationAdministration.request</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest)
+    <t xml:space="preserve">Reference(MedicationRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -1305,7 +1305,7 @@
     <t>MedicationAdministration.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device)
+    <t xml:space="preserve">Reference(Device|4.0.1)
 </t>
   </si>
   <si>
@@ -1491,7 +1491,7 @@
     <t>bodySite</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {bodySite|5.3.0-ballot-tc1}
+    <t xml:space="preserve">Extension {bodySite|5.2.0}
 </t>
   </si>
   <si>
@@ -1630,7 +1630,7 @@
     <t>薬剤が投与される方法を記述する暗号化された概念。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/administration-method-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/administration-method-codes|4.0.1</t>
   </si>
   <si>
     <t>.methodCode</t>
@@ -1910,7 +1910,7 @@
   </si>
   <si>
     <t>Ratio
-Quantity {SimpleQuantity}</t>
+Quantity {SimpleQuantity|4.0.1}</t>
   </si>
   <si>
     <t>単位時間あたりの用量</t>
@@ -1971,7 +1971,7 @@
     <t>MedicationAdministration.eventHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.0.1)
 </t>
   </si>
   <si>

--- a/jpcore-r4/main/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
